--- a/Project-7 ---/V3/Data/cancer_data_imputed.Farhana.xlsx
+++ b/Project-7 ---/V3/Data/cancer_data_imputed.Farhana.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Freelance\Statistical-Analysis\Project-7 ---\V3\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Statistical-Analysis\Project-7 ---\V3\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F58183-4AC6-4D59-ACCA-400274DCEFC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9765" yWindow="60" windowWidth="17250" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9765" yWindow="60" windowWidth="17250" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -23,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11249" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11249" uniqueCount="258">
   <si>
     <t>mobile</t>
   </si>
@@ -796,16 +795,13 @@
     <t>negative</t>
   </si>
   <si>
-    <t>Biopsy</t>
-  </si>
-  <si>
     <t>No Surgery</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1138,7 +1134,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:DA136"/>
   <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2739,7 +2735,7 @@
         <v>107</v>
       </c>
       <c r="AT6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AU6" t="s">
         <v>118</v>
@@ -5582,7 +5578,7 @@
         <v>111</v>
       </c>
       <c r="AT16" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU16" t="s">
         <v>118</v>
@@ -5872,7 +5868,7 @@
         <v>107</v>
       </c>
       <c r="AT17" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU17" t="s">
         <v>118</v>
@@ -6165,7 +6161,7 @@
         <v>107</v>
       </c>
       <c r="AT18" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AU18" t="s">
         <v>118</v>
@@ -6452,7 +6448,7 @@
         <v>107</v>
       </c>
       <c r="AT19" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AU19" t="s">
         <v>118</v>
@@ -7322,7 +7318,7 @@
         <v>107</v>
       </c>
       <c r="AT22" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AU22" t="s">
         <v>118</v>
@@ -7609,7 +7605,7 @@
         <v>111</v>
       </c>
       <c r="AT23" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU23" t="s">
         <v>118</v>
@@ -8195,7 +8191,7 @@
         <v>111</v>
       </c>
       <c r="AT25" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU25" t="s">
         <v>118</v>
@@ -8482,7 +8478,7 @@
         <v>107</v>
       </c>
       <c r="AT26" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU26" t="s">
         <v>118</v>
@@ -8769,7 +8765,7 @@
         <v>111</v>
       </c>
       <c r="AT27" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU27" t="s">
         <v>118</v>
@@ -9059,7 +9055,7 @@
         <v>107</v>
       </c>
       <c r="AT28" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU28" t="s">
         <v>118</v>
@@ -9642,7 +9638,7 @@
         <v>111</v>
       </c>
       <c r="AT30" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU30" t="s">
         <v>118</v>
@@ -10225,7 +10221,7 @@
         <v>111</v>
       </c>
       <c r="AT32" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU32" t="s">
         <v>118</v>
@@ -10509,7 +10505,7 @@
         <v>107</v>
       </c>
       <c r="AT33" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU33" t="s">
         <v>118</v>
@@ -10799,7 +10795,7 @@
         <v>111</v>
       </c>
       <c r="AT34" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU34" t="s">
         <v>118</v>
@@ -11385,7 +11381,7 @@
         <v>111</v>
       </c>
       <c r="AT36" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU36" t="s">
         <v>118</v>
@@ -11669,7 +11665,7 @@
         <v>111</v>
       </c>
       <c r="AT37" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU37" t="s">
         <v>118</v>
@@ -11950,7 +11946,7 @@
         <v>107</v>
       </c>
       <c r="AT38" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU38" t="s">
         <v>118</v>
@@ -12808,7 +12804,7 @@
         <v>107</v>
       </c>
       <c r="AT41" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU41" t="s">
         <v>118</v>
@@ -13101,7 +13097,7 @@
         <v>111</v>
       </c>
       <c r="AT42" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU42" t="s">
         <v>118</v>
@@ -13391,7 +13387,7 @@
         <v>107</v>
       </c>
       <c r="AT43" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU43" t="s">
         <v>118</v>
@@ -13965,7 +13961,7 @@
         <v>111</v>
       </c>
       <c r="AT45" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU45" t="s">
         <v>118</v>
@@ -14536,7 +14532,7 @@
         <v>111</v>
       </c>
       <c r="AT47" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU47" t="s">
         <v>118</v>
@@ -15119,7 +15115,7 @@
         <v>107</v>
       </c>
       <c r="AT49" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU49" t="s">
         <v>118</v>
@@ -15403,7 +15399,7 @@
         <v>111</v>
       </c>
       <c r="AT50" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU50" t="s">
         <v>118</v>
@@ -16572,7 +16568,7 @@
         <v>107</v>
       </c>
       <c r="AT54" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU54" t="s">
         <v>118</v>
@@ -17442,7 +17438,7 @@
         <v>111</v>
       </c>
       <c r="AT57" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU57" t="s">
         <v>118</v>
@@ -17723,7 +17719,7 @@
         <v>111</v>
       </c>
       <c r="AT58" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU58" t="s">
         <v>118</v>
@@ -20339,7 +20335,7 @@
         <v>107</v>
       </c>
       <c r="AT67" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AU67" t="s">
         <v>118</v>
@@ -21203,7 +21199,7 @@
         <v>111</v>
       </c>
       <c r="AT70" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AU70" t="s">
         <v>118</v>
@@ -25846,7 +25842,7 @@
         <v>107</v>
       </c>
       <c r="AT86" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AU86" t="s">
         <v>118</v>
@@ -34836,7 +34832,7 @@
         <v>111</v>
       </c>
       <c r="AT117" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU117" t="s">
         <v>118</v>
@@ -35407,7 +35403,7 @@
         <v>111</v>
       </c>
       <c r="AT119" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AU119" t="s">
         <v>118</v>
@@ -35697,7 +35693,7 @@
         <v>111</v>
       </c>
       <c r="AT120" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU120" t="s">
         <v>118</v>
@@ -36561,7 +36557,7 @@
         <v>111</v>
       </c>
       <c r="AT123" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AU123" t="s">
         <v>118</v>
@@ -36848,7 +36844,7 @@
         <v>111</v>
       </c>
       <c r="AT124" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU124" t="s">
         <v>118</v>
@@ -38588,7 +38584,7 @@
         <v>107</v>
       </c>
       <c r="AT130" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AU130" t="s">
         <v>118</v>
@@ -38875,7 +38871,7 @@
         <v>111</v>
       </c>
       <c r="AT131" t="s">
-        <v>257</v>
+        <v>137</v>
       </c>
       <c r="AU131" t="s">
         <v>118</v>
@@ -40319,7 +40315,7 @@
         <v>107</v>
       </c>
       <c r="AT136" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AU136" t="s">
         <v>118</v>
@@ -40491,6 +40487,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:DA136"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
